--- a/XLibur.Tests/Resource/Examples/AutoFilter/DateTimeGroupAutoFilter.xlsx
+++ b/XLibur.Tests/Resource/Examples/AutoFilter/DateTimeGroupAutoFilter.xlsx
@@ -380,7 +380,7 @@
   <x:dimension ref="A1:A7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.139196" style="1" customWidth="1"/>
+    <x:col min="1" max="1" width="14.424911" style="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
